--- a/data/trans_orig/IP22-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73053</t>
+          <t>72757</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83559</t>
+          <t>83659</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67222</t>
+          <t>67266</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78635</t>
+          <t>78265</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>144207</t>
+          <t>144333</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159254</t>
+          <t>159014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17814</t>
+          <t>18110</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18935</t>
+          <t>18965</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17977</t>
+          <t>18262</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33005</t>
+          <t>32871</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>315015</t>
+          <t>313796</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341130</t>
+          <t>340566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357620</t>
+          <t>358819</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>387167</t>
+          <t>385883</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>678162</t>
+          <t>682886</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>720931</t>
+          <t>722872</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74957</t>
+          <t>75521</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101072</t>
+          <t>102291</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88607</t>
+          <t>90394</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118613</t>
+          <t>117262</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>171630</t>
+          <t>169860</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>213600</t>
+          <t>209701</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>132359</t>
+          <t>132452</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>149152</t>
+          <t>149758</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>109121</t>
+          <t>109004</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>126152</t>
+          <t>126560</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>248048</t>
+          <t>246700</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>272504</t>
+          <t>270536</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,44%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23679</t>
+          <t>22994</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39933</t>
+          <t>39990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29769</t>
+          <t>29450</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46292</t>
+          <t>46531</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57041</t>
+          <t>58642</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80410</t>
+          <t>82437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>532737</t>
+          <t>532651</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>566201</t>
+          <t>566210</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>545105</t>
+          <t>545834</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>581744</t>
+          <t>582010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1091640</t>
+          <t>1085634</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1138494</t>
+          <t>1137644</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>114159</t>
+          <t>113439</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>147599</t>
+          <t>147250</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>137506</t>
+          <t>137080</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>173355</t>
+          <t>171930</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>260326</t>
+          <t>261697</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>305595</t>
+          <t>311758</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63907</t>
+          <t>64429</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77372</t>
+          <t>77686</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51241</t>
+          <t>51076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65665</t>
+          <t>65291</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120188</t>
+          <t>119046</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139892</t>
+          <t>138679</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,04%</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14997</t>
+          <t>14683</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28462</t>
+          <t>27940</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19313</t>
+          <t>19564</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33302</t>
+          <t>33970</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>38303</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56656</t>
+          <t>57580</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>331659</t>
+          <t>330789</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>361594</t>
+          <t>361449</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336533</t>
+          <t>337016</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370496</t>
+          <t>369882</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>677828</t>
+          <t>678921</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>723642</t>
+          <t>724371</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8785</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11153</t>
+          <t>11489</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89028</t>
+          <t>88739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118125</t>
+          <t>119217</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117525</t>
+          <t>117778</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>151143</t>
+          <t>150676</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>215905</t>
+          <t>213937</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>260607</t>
+          <t>259168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>115622</t>
+          <t>115528</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>134000</t>
+          <t>134447</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121046</t>
+          <t>119972</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>138764</t>
+          <t>138468</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>240128</t>
+          <t>241642</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>267789</t>
+          <t>267341</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29622</t>
+          <t>29926</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48563</t>
+          <t>48111</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31873</t>
+          <t>32509</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49828</t>
+          <t>50340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67440</t>
+          <t>67166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94780</t>
+          <t>92972</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>523584</t>
+          <t>523740</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>561139</t>
+          <t>562683</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>522608</t>
+          <t>522162</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>562576</t>
+          <t>565479</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1056566</t>
+          <t>1056659</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1112789</t>
+          <t>1109742</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,99%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16404</t>
+          <t>17047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>145830</t>
+          <t>144218</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>183558</t>
+          <t>182195</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>179961</t>
+          <t>178516</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>220555</t>
+          <t>220225</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>336862</t>
+          <t>340472</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>391366</t>
+          <t>394626</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>43277</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52906</t>
+          <t>53459</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55596</t>
+          <t>55669</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64182</t>
+          <t>64515</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102251</t>
+          <t>102427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115515</t>
+          <t>114836</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16236</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12168</t>
+          <t>12354</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12077</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24882</t>
+          <t>24518</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>377996</t>
+          <t>377036</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404535</t>
+          <t>404446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>392455</t>
+          <t>390456</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>419776</t>
+          <t>418354</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>779083</t>
+          <t>778597</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>816547</t>
+          <t>815607</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11944</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>12133</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61315</t>
+          <t>61479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86525</t>
+          <t>86716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68959</t>
+          <t>70381</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96280</t>
+          <t>98279</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137291</t>
+          <t>138337</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175438</t>
+          <t>174627</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>129896</t>
+          <t>130711</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146559</t>
+          <t>147381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143154</t>
+          <t>143514</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>161140</t>
+          <t>160733</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>278444</t>
+          <t>278944</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>302855</t>
+          <t>303508</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>755</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25620</t>
+          <t>24962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41826</t>
+          <t>41461</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23385</t>
+          <t>23182</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40577</t>
+          <t>39904</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53399</t>
+          <t>53422</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77470</t>
+          <t>77007</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>561168</t>
+          <t>564245</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>594746</t>
+          <t>595776</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>601367</t>
+          <t>602335</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>635723</t>
+          <t>635749</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1175115</t>
+          <t>1176799</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1220500</t>
+          <t>1224153</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>13137</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>102190</t>
+          <t>101910</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134076</t>
+          <t>131857</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>105714</t>
+          <t>105517</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>139984</t>
+          <t>138030</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>216644</t>
+          <t>214536</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>262404</t>
+          <t>260543</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28190</t>
+          <t>29258</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50721</t>
+          <t>51032</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43607</t>
+          <t>43548</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55436</t>
+          <t>55523</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79577</t>
+          <t>79461</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103383</t>
+          <t>103087</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>25420</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>18456</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>13595</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37105</t>
+          <t>37221</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>381168</t>
+          <t>381926</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>409395</t>
+          <t>410032</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>427607</t>
+          <t>426750</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>457902</t>
+          <t>458299</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>818367</t>
+          <t>817169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>859320</t>
+          <t>859310</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49576</t>
+          <t>48939</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77803</t>
+          <t>77045</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58717</t>
+          <t>58320</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89012</t>
+          <t>89869</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116270</t>
+          <t>116280</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157223</t>
+          <t>158421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111284</t>
+          <t>109915</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>128178</t>
+          <t>126638</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>140922</t>
+          <t>139844</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160120</t>
+          <t>159991</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>257887</t>
+          <t>257833</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>282775</t>
+          <t>282485</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>22913</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38267</t>
+          <t>39636</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>23358</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42427</t>
+          <t>43505</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50125</t>
+          <t>50415</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75013</t>
+          <t>75067</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>537692</t>
+          <t>536382</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>577516</t>
+          <t>577987</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>623942</t>
+          <t>626659</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>662328</t>
+          <t>662355</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1171886</t>
+          <t>1174559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1230731</t>
+          <t>1232301</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,47%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85684</t>
+          <t>85213</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>125508</t>
+          <t>126818</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99644</t>
+          <t>99617</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>138030</t>
+          <t>135313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>194441</t>
+          <t>192871</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>253286</t>
+          <t>250613</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>73286</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>67025</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>78104</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>84,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>77,18%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>89,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>78786</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>72757</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>83659</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>72265</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>82915</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>86,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>80,07%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>92,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>73286</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>67266</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>78265</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>84,39%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>144333</t>
+          <t>143557</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159014</t>
+          <t>159331</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,66%</t>
         </is>
       </c>
     </row>
@@ -836,107 +836,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3235</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>648</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2625</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3424</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3238</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -949,72 +949,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12911</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8196</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19089</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>9,44%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>21,98%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>12081</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7208</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18110</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>7952</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>18602</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>13,29%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,93%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12911</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8123</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>18965</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18262</t>
+          <t>17977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32871</t>
+          <t>33558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>373409</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>357156</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>386326</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>78,28%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>80,99%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>494</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>329005</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>313796</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>340566</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>314967</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>340298</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>79,07%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,85%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>373409</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>358819</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>385883</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>78,28%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>682886</t>
+          <t>682891</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>722872</t>
+          <t>722781</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -1292,107 +1292,107 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3395</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>680</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>3839</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>3082</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -1405,72 +1405,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>102902</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>89945</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>119037</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,57%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18,86%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>87082</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>75521</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>102291</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>75789</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>101120</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>20,93%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>102902</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>90394</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>117262</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,57%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169860</t>
+          <t>169395</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>209701</t>
+          <t>209171</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1635,72 +1635,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>118250</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>109004</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>126403</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>74,78%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>68,93%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>79,93%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>141568</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>132452</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149758</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>148867</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>81,33%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>76,09%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>86,04%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>118250</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>109004</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>126560</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>74,78%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>246700</t>
+          <t>246573</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>270536</t>
+          <t>270928</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -1748,72 +1748,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5221</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1278</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4215</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4505</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1934</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5426</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1861,72 +1861,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37954</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>30483</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>47566</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19,28%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>30,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>31220</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>22994</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>39990</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>23566</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>40055</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>17,94%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,97%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>37954</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>29450</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>46531</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>24,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58642</t>
+          <t>58653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82437</t>
+          <t>82078</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2091,72 +2091,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>564945</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>547418</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>582340</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>78,25%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>75,82%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>80,66%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>817</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>549360</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>532651</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>566210</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>531849</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>564820</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>80,67%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>78,21%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>83,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>564945</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>545834</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>582010</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>78,25%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1085634</t>
+          <t>1089656</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1137644</t>
+          <t>1140861</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,32%</t>
         </is>
       </c>
     </row>
@@ -2204,72 +2204,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3262</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1269</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7133</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>1278</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4208</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4498</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3262</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1285</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>7183</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9429</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2317,72 +2317,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>153767</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>136819</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>171715</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>21,3%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>18,95%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>23,78%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>130383</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>113439</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>147250</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>114777</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>147353</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>19,15%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>21,62%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>153767</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>137080</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>171930</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>21,3%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>261697</t>
+          <t>259202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>311758</t>
+          <t>308631</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2610,7 +2610,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>58507</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50824</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>65467</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>68,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>59,56%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>76,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>71258</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>64429</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>77686</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>64574</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>77715</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>77,14%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>69,75%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>84,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>58507</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>51076</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>65291</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>68,56%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119046</t>
+          <t>119267</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138679</t>
+          <t>139953</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,76%</t>
         </is>
       </c>
     </row>
@@ -2891,107 +2891,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3940</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>787</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3987</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>787</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3929</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -3004,72 +3004,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>26041</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19284</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>33881</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>30,52%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>22,6%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>39,7%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>21111</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>14683</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>27940</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>14654</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>27795</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>22,86%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15,9%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>30,25%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>26041</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>19564</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>33970</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>30,52%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38303</t>
+          <t>37296</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57580</t>
+          <t>57111</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -3117,57 +3117,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>85335</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>85335</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>85335</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>85335</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>85335</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>85335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>354477</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>337381</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>372059</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>72,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>68,55%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>501</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>346515</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>330789</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>361449</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>330865</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>361338</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>76,74%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>354477</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>337016</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>369882</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>72,03%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>678921</t>
+          <t>678947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>724371</t>
+          <t>722776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,59%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4175</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>8818</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>1484</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4522</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4543</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>4175</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1629</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>8694</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11489</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>133494</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>117046</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>150303</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>27,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>23,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>30,54%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>103565</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>88739</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>119217</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>88600</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>119002</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>22,93%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,65%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>133494</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>117778</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>150676</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>27,12%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>213937</t>
+          <t>215485</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>259168</t>
+          <t>258790</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>492147</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>492147</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>492147</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>451565</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>451565</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>451565</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>492147</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>492147</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>492147</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>129908</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>119481</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139160</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>75,43%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>69,37%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>80,8%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>125155</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>115528</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>134447</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>115398</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>133673</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>75,03%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>69,26%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>80,6%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>129908</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>119972</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>138468</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>75,43%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>241642</t>
+          <t>240038</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>267341</t>
+          <t>267863</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1443</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4362</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2636</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>816</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6283</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6564</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1443</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5308</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>40877</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>31612</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>50254</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>23,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>18,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>29,18%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>39021</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>29926</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>48111</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>30693</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>48801</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>23,39%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>17,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>28,84%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>40877</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>32509</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>50340</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>23,73%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67166</t>
+          <t>67791</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92972</t>
+          <t>94491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>776</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>542893</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>521805</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>562887</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>72,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69,6%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>75,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>781</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>542928</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>523740</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>562683</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>524280</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>559651</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>76,39%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>73,69%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>79,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>542893</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>522162</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>565479</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>72,41%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1056659</t>
+          <t>1058549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1109742</t>
+          <t>1114520</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,31%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6405</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3158</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11491</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>4121</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1602</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8262</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>8884</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>6405</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3181</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>12424</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17047</t>
+          <t>17665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>200412</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>180595</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>221060</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>26,73%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>24,09%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>29,49%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>163697</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>144218</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>182195</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>145838</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>181844</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>23,03%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>20,29%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>25,63%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>200412</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>178516</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>220225</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>26,73%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>340472</t>
+          <t>335307</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>394626</t>
+          <t>391405</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1069</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>749710</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>749710</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>749710</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>710746</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>710746</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>710746</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>749710</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>749710</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>749710</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4665,7 +4665,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4833,72 +4833,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>60547</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>55446</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>64383</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>88,24%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>80,81%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>93,83%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>49094</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>43277</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53459</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>43245</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>53145</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>82,68%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>72,88%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>90,03%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>60547</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>55669</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>64515</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>88,24%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102427</t>
+          <t>102230</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114836</t>
+          <t>114917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -4946,107 +4946,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3850</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>665</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3310</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3925</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3357</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -5059,72 +5059,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3748</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12035</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>17,54%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>10284</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5919</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16101</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6233</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>16133</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>17,32%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,97%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>27,12%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7402</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3974</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12354</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24518</t>
+          <t>25043</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -5172,57 +5172,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5289,72 +5289,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>406394</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>390768</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>419283</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,95%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,79%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>589</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>392212</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>377036</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>404446</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>379000</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>405258</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>83,04%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,83%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>85,64%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>406394</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>390456</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>418354</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>83,15%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>778597</t>
+          <t>776332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>815607</t>
+          <t>816091</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -5402,72 +5402,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>6950</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3488</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>12395</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>3526</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>12406</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>1,47%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>11908</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -5515,72 +5515,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>82341</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>69452</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>97967</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,85%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,05%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>73128</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>61479</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>86716</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>60946</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>86173</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>15,48%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>82341</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>70381</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>98279</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,85%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138337</t>
+          <t>139439</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174627</t>
+          <t>177193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -5628,57 +5628,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5745,72 +5745,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>152557</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>142966</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>160588</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>81,72%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>76,58%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>86,02%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>138981</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>130711</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>147381</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>130329</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>146611</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>80,47%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>75,69%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>85,34%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>152557</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>143514</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>160733</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>81,72%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>278944</t>
+          <t>280578</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>303508</t>
+          <t>304465</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,72%</t>
         </is>
       </c>
     </row>
@@ -5858,72 +5858,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2678</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6130</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2717</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3659</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2678</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>755</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6450</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -5971,72 +5971,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>31441</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24083</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>40816</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,84%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>21,86%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>33094</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24962</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>41461</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>25259</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>41614</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>19,16%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>14,45%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>24,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>31441</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>23182</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>39904</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>16,84%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53422</t>
+          <t>52055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77007</t>
+          <t>75365</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -6084,57 +6084,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>186677</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>186677</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>186677</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>186677</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>186677</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>186677</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6201,72 +6201,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>619499</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>601688</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>636071</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>83,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>80,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>85,49%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>867</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>580287</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>564245</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>595776</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>564188</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>595512</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>82,38%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>80,11%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>84,58%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>886</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>619499</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>602335</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>635749</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>83,26%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1176799</t>
+          <t>1175764</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1224153</t>
+          <t>1221945</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -6314,72 +6314,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3343</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7506</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>7578</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>4018</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>13137</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3611</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>12120</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3343</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1051</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>7293</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>17525</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -6427,72 +6427,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>121184</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>105131</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>138871</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>16,29%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>14,13%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>18,66%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>116506</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>101910</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>131857</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>101108</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>131729</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>16,54%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>14,47%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,72%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>121184</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>105517</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>138030</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>16,29%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>214536</t>
+          <t>216013</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>260543</t>
+          <t>261258</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -6540,57 +6540,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>744026</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>744026</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>744026</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>744026</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>744026</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>744026</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6720,7 +6720,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6888,72 +6888,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46939</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40208</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>50996</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>82,74%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>70,87%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>89,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>44018</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>29258</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>51032</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>80,5%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>53,51%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>50631</t>
+          <t>40974</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43548</t>
+          <t>36746</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55523</t>
+          <t>43835</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>94649</t>
+          <t>87913</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79461</t>
+          <t>79478</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103087</t>
+          <t>93404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9793</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5736</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16524</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>17,26%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>29,13%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>10660</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3646</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>25420</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19,5%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>46,49%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18456</t>
+          <t>10012</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>22033</t>
+          <t>15577</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37221</t>
+          <t>24012</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -7227,57 +7227,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7344,72 +7344,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>408705</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>393078</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>421829</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>549</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>396045</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>381926</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>410032</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>86,29%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>562</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>443398</t>
+          <t>370861</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426750</t>
+          <t>358402</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>458299</t>
+          <t>382841</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>839443</t>
+          <t>779566</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>817169</t>
+          <t>761192</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>859310</t>
+          <t>799253</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,16%</t>
         </is>
       </c>
     </row>
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>66973</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>53849</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>82600</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>62926</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>48939</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>77045</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,71%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,66%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>73221</t>
+          <t>60045</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58320</t>
+          <t>48065</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89869</t>
+          <t>72504</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>136147</t>
+          <t>127018</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116280</t>
+          <t>107331</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158421</t>
+          <t>145392</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -7683,57 +7683,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>458971</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>458971</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>458971</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>430906</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>430906</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>430906</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>975590</t>
+          <t>906584</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>975590</t>
+          <t>906584</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>975590</t>
+          <t>906584</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7800,72 +7800,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139563</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>129177</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>147467</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>82,87%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>76,7%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>87,56%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>119902</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>109915</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>126638</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>80,17%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>73,5%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>84,68%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>151105</t>
+          <t>120017</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>139844</t>
+          <t>111072</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>159991</t>
+          <t>127215</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>271007</t>
+          <t>259581</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>257833</t>
+          <t>246295</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>282485</t>
+          <t>270381</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -8026,72 +8026,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28856</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20952</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>39242</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17,13%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>23,3%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>29649</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>22913</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>39636</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19,83%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>26,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32244</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23358</t>
+          <t>22761</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43505</t>
+          <t>38904</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>61893</t>
+          <t>58814</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50415</t>
+          <t>48014</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75067</t>
+          <t>72100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -8139,57 +8139,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8256,72 +8256,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>595207</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>575669</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>610241</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>84,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>82,14%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>87,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>791</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>559965</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>536382</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>577987</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>84,43%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>80,88%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>87,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>645134</t>
+          <t>531853</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>626659</t>
+          <t>516640</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>662355</t>
+          <t>546743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1205099</t>
+          <t>1127060</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1174559</t>
+          <t>1102391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1232301</t>
+          <t>1151047</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,64%</t>
         </is>
       </c>
     </row>
@@ -8482,72 +8482,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>105622</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>90588</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>125160</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15,07%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>12,93%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>17,86%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>103235</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>85213</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>126818</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>15,57%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>12,85%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>19,12%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>116838</t>
+          <t>95787</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99617</t>
+          <t>80897</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>135313</t>
+          <t>111000</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>220073</t>
+          <t>201409</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>192871</t>
+          <t>177422</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>250613</t>
+          <t>226078</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -8595,57 +8595,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>663200</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>663200</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>663200</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>627640</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>627640</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>627640</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1425172</t>
+          <t>1328469</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1425172</t>
+          <t>1328469</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1425172</t>
+          <t>1328469</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
